--- a/lessons/chess/excels/remarks.xlsx
+++ b/lessons/chess/excels/remarks.xlsx
@@ -504,12 +504,12 @@
     </comment>
     <comment ref="J48" authorId="0" shapeId="0">
       <text>
-        <t>+" (00:00:00), +" (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), += (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +\ (00:00:00), +cell (00:00:00), +chess (00:00:00), +class (00:00:00), +class (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +handleclick (00:00:00), +head (00:00:00), +light (00:00:00), +light (00:00:00), +light (00:00:00), +light (00:00:00), +light (00:00:00), +style (00:00:00), -Chess (11:56:36.040), -dark (11:58:37.525), -dark (12:08:25.473), -dark (12:08:30.373), -dark (12:08:35.273), -display (12:24:00.258), -: (12:24:00.330), -flex (12:24:01.038), -; (12:24:01.089), -align (12:24:02.090), -- (12:24:02.167), -items (12:24:02.854), -: (12:24:02.925), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -; (12:24:07.221), -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -&gt; (12:25:38.438), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -) (12:52:12.282), -let (12:56:53.102)</t>
+        <t>+" (00:00:00), +" (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), += (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +\ (00:00:00), +cell (00:00:00), +chess (00:00:00), +class (00:00:00), +class (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +handleclick (00:00:00), +head (00:00:00), +light (00:00:00), +light (00:00:00), +light (00:00:00), +light (00:00:00), +light (00:00:00), +style (00:00:00), -Chess (11:56:36.040), -/ (11:56:37.399), -dark (11:58:37.525), -dark (12:08:25.473), -dark (12:08:30.373), -dark (12:08:35.273), -display (12:24:00.258), -: (12:24:00.330), -flex (12:24:01.038), -; (12:24:01.089), -align (12:24:02.090), -- (12:24:02.167), -items (12:24:02.854), -: (12:24:02.925), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -; (12:24:07.221), -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -&gt; (12:25:38.438), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -) (12:52:12.282), -let (12:56:53.102)</t>
       </text>
     </comment>
     <comment ref="M48" authorId="0" shapeId="0">
       <text>
-        <t>-Chess (11:56:36.040) ~0.80, -dark (11:58:37.525) ~0.00, -dark (12:08:25.473) ~0.00, -dark (12:08:30.373) ~0.00, -dark (12:08:35.273) ~0.00, -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -&gt; (12:25:38.438), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +&lt; (00:00:00), +/ (00:00:00), +style (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +head (00:00:00), +&gt; (00:00:00), +chess (00:00:00), +handleclick (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +class (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +light (00:00:00), +\ (00:00:00), +light (00:00:00), +light (00:00:00), +light (00:00:00)</t>
+        <t>-Chess (11:56:36.040) ~0.80, -/ (11:56:37.399), -dark (11:58:37.525) ~0.00, -dark (12:08:25.473) ~0.00, -dark (12:08:30.373) ~0.00, -dark (12:08:35.273) ~0.00, -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -&gt; (12:25:38.438), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +&lt; (00:00:00), +/ (00:00:00), +style (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +head (00:00:00), +&gt; (00:00:00), +chess (00:00:00), +handleclick (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +class (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +light (00:00:00), +\ (00:00:00), +light (00:00:00), +light (00:00:00), +light (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O48" authorId="0" shapeId="0">
@@ -3007,19 +3007,19 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>93</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>+" (00:00:00), +" (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), += (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +\ (00:00:00), +cell (00:00:00), +chess (00:00:00), +class (00:00:00), +class (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +handleclick (00:00:00), +head (00:00:00), +light (00:00:00), +light (00:00:00), +light (00:00:00), +light (00:00:00), +light (00:00:00), +style (00:00:00), -Chess (11:56:36.040), -dark (11:58:37.525), -dark (12:08:25.473), -dark (12:08:30.373), -dark (12:08:35.273), -display (12:24:00.258), -: (12:24:00.330), -flex (12:24:01.038), -; (12:24:01.089), -align (12:24:02.090), -- (12:24:02.167), -items (12:24:02.854), -: (12:24:02.925), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -; (12:24:07.221), -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -&gt; (12:25:38.438), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -) (12:52:12.282), -let (12:56:53.102)</t>
+          <t>+" (00:00:00), +" (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), += (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +\ (00:00:00), +cell (00:00:00), +chess (00:00:00), +class (00:00:00), +class (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +handleclick (00:00:00), +head (00:00:00), +light (00:00:00), +light (00:00:00), +light (00:00:00), +light (00:00:00), +light (00:00:00), +style (00:00:00), -Chess (11:56:36.040), -/ (11:56:37.399), -dark (11:58:37.525), -dark (12:08:25.473), -dark (12:08:30.373), -dark (12:08:35.273), -display (12:24:00.258), -: (12:24:00.330), -flex (12:24:01.038), -; (12:24:01.089), -align (12:24:02.090), -- (12:24:02.167), -items (12:24:02.854), -: (12:24:02.925), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -; (12:24:07.221), -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -&gt; (12:25:38.438), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -) (12:52:12.282), -let (12:56:53.102)</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>93.59999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>-Chess (11:56:36.040) ~0.80, -dark (11:58:37.525) ~0.00, -dark (12:08:25.473) ~0.00, -dark (12:08:30.373) ~0.00, -dark (12:08:35.273) ~0.00, -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -&gt; (12:25:38.438), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +&lt; (00:00:00), +/ (00:00:00), +style (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +head (00:00:00), +&gt; (00:00:00), +chess (00:00:00), +handleclick (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +class (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +light (00:00:00), +\ (00:00:00), +light (00:00:00), +light (00:00:00), +light (00:00:00)</t>
+          <t>-Chess (11:56:36.040) ~0.80, -/ (11:56:37.399), -dark (11:58:37.525) ~0.00, -dark (12:08:25.473) ~0.00, -dark (12:08:30.373) ~0.00, -dark (12:08:35.273) ~0.00, -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -&gt; (12:25:38.438), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), +"* (12:49:43.795), +;* (12:49:44.003), +)* (12:49:44.302), +this* (12:49:45.208), +(* (12:49:45.400), +"* (12:49:47.810), +=* (12:49:48.009), +onclick* (12:49:49.458), +&lt; (00:00:00), +/ (00:00:00), +style (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +head (00:00:00), +&gt; (00:00:00), +chess (00:00:00), +handleclick (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +class (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +light (00:00:00), +\ (00:00:00), +light (00:00:00), +light (00:00:00), +light (00:00:00)</t>
         </is>
       </c>
       <c r="O48" t="n">
